--- a/__Master-Application-Packet/01_CNA_CDPH_CE_PACKET/LMS_Build_Modules_10_17/CNA_Recert_Modules_10_17_24HR_LMS_BUILD_WORKBOOK.xlsx
+++ b/__Master-Application-Packet/01_CNA_CDPH_CE_PACKET/LMS_Build_Modules_10_17/CNA_Recert_Modules_10_17_24HR_LMS_BUILD_WORKBOOK.xlsx
@@ -464,431 +464,688 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Course_Map - 24-Hour CNA Recertification Online CE (Modules 10-17)</t>
+          <t>Course_Map - 24-Hour CNA Recertification Online CE (12 units x 2 hours)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>DRAFT / PENDING APPROVAL - Do not advertise, issue certificates, or represent this course as approved until approval status, provider/course identifiers, and certificate wording are confirmed. Online CE only; not clinical hours. Fictional data only; no PHI.</t>
+          <t>DRAFT / PENDING APPROVAL - Do not advertise, issue certificates, or represent this course as approved until approval status, provider/course identifiers, and certificate wording are confirmed. Online CE only; no clinical hours. 12 units x 2 online CE hours = 24. Source backbone: Modules 10-17. Fictional data only; no PHI.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>Unit ID</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Unit Title</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Online CE Hours</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Source Module #</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Source Module Title</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Online CE Hours</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Estimated Minutes</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Source Reference</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Completion Requirement</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Evidence Artifact</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>SME/Compliance Flag</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>U01</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Vital Signs I: Purpose, Terminology, Temperature, and Pain Observation</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>Vital Signs</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>180</v>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>ContentV2/survey-evidence/_source_text/module-10.txt</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>All lessons viewed + knowledge check attempted + scenario completed + documentation exercise submitted</t>
-        </is>
-      </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Activity-completion timestamps, KC attempt record, scenario branch log, submitted simulated artifact, time-in-module log</t>
+          <t>All lessons viewed + knowledge check attempted + scenario completed + documentation/reflection submitted</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Confirm normal-range values; no hands-on competency implied</t>
+          <t>Activity-completion timestamps, KC attempt record, scenario branch log, submitted simulated artifact, time-in-unit log</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Confirm normal-range values; observe/report level only (no hands-on competency)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>U02</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Vital Signs II: Pulse, Respirations, Blood Pressure, Recording, and Reporting</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Vital Signs</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>ContentV2/survey-evidence/_source_text/module-10.txt</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>All lessons viewed + knowledge check attempted + scenario completed + documentation/reflection submitted</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Activity-completion timestamps, KC attempt record, scenario branch log, submitted simulated artifact, time-in-unit log</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>Confirm BP/pulse/resp ranges; recording within CNA scope; report abnormal findings</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>U03</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Nutrition, Hydration, Diets, Feeding Assistance, and Aspiration Awareness</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Nutrition</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>180</v>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>ContentV2/survey-evidence/_source_text/module-11.txt</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>All lessons viewed + knowledge check attempted + scenario completed + documentation exercise submitted</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Activity-completion timestamps, KC attempt record, scenario branch log, submitted simulated artifact, time-in-module log</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Confirm therapeutic-diet list vs facility diet manual; assistance level only</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>All lessons viewed + knowledge check attempted + scenario completed + documentation/reflection submitted</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>Activity-completion timestamps, KC attempt record, scenario branch log, submitted simulated artifact, time-in-unit log</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>Confirm therapeutic-diet list vs facility manual; feeding at assistance level; aspiration precautions</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>U04</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Emergency Procedures, Distress Recognition, Choking Response, and Facility Codes</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Emergency Procedures</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>180</v>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>ContentV2/survey-evidence/_source_text/module-12.txt</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>All lessons viewed + knowledge check attempted + scenario completed + documentation exercise submitted</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>Activity-completion timestamps, KC attempt record, scenario branch log, submitted simulated artifact, time-in-module log</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>HIGH: state no hands-on CPR/Heimlich competency; confirm code list/AHA-ARC</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>All lessons viewed + knowledge check attempted + scenario completed + documentation/reflection submitted</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Activity-completion timestamps, KC attempt record, scenario branch log, submitted simulated artifact, time-in-unit log</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>HIGH: state no hands-on CPR/Heimlich competency; confirm facility codes/AHA-ARC language</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>U05</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Long Term Care Patient/Resident I: Aging, Body Systems, and Common Conditions</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>Long Term Care Patient/Resident</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>180</v>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>ContentV2/survey-evidence/_source_text/module-13.txt</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>All lessons viewed + knowledge check attempted + scenario completed + documentation exercise submitted</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Activity-completion timestamps, KC attempt record, scenario branch log, submitted simulated artifact, time-in-module log</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>Confirm person-centered dementia language; CNA scope (no diagnosis)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>All lessons viewed + knowledge check attempted + scenario completed + documentation/reflection submitted</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>Activity-completion timestamps, KC attempt record, scenario branch log, submitted simulated artifact, time-in-unit log</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Confirm aging/A&amp;P content; complications of immobility at observe/report level</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>U06</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Long Term Care Patient/Resident II: Dementia-Sensitive Care, Psychosocial Needs, and Community Resources</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="E10" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Long Term Care Patient/Resident</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>ContentV2/survey-evidence/_source_text/module-13.txt</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>All lessons viewed + knowledge check attempted + scenario completed + documentation/reflection submitted</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Activity-completion timestamps, KC attempt record, scenario branch log, submitted simulated artifact, time-in-unit log</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>Confirm person-centered dementia language; CNA scope (no behavioral diagnosis)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>U07</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Rehabilitative Nursing and Restorative Care</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>Rehabilitative Nursing</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>180</v>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>ContentV2/survey-evidence/_source_text/module-14.txt</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>All lessons viewed + knowledge check attempted + scenario completed + documentation exercise submitted</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>Activity-completion timestamps, KC attempt record, scenario branch log, submitted simulated artifact, time-in-module log</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>All lessons viewed + knowledge check attempted + scenario completed + documentation/reflection submitted</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>Activity-completion timestamps, KC attempt record, scenario branch log, submitted simulated artifact, time-in-unit log</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>ROM/restorative at assist/observe level only; confirm device list</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>U08</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Observation and Charting I: Objective/Subjective Observation, Terminology, and Reporting Cues</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>Observation and Charting</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>180</v>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>ContentV2/survey-evidence/_source_text/module-15.txt</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>All lessons viewed + knowledge check attempted + scenario completed + documentation exercise submitted</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>Activity-completion timestamps, KC attempt record, scenario branch log, submitted simulated artifact, time-in-module log</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>All lessons viewed + knowledge check attempted + scenario completed + documentation/reflection submitted</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>Activity-completion timestamps, KC attempt record, scenario branch log, submitted simulated artifact, time-in-unit log</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>Objective vs subjective accuracy; reporting cues within scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>U09</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Observation and Charting II: Charting Documents, Legal Documentation, and Change Reporting</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Observation and Charting</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>ContentV2/survey-evidence/_source_text/module-15.txt</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>All lessons viewed + knowledge check attempted + scenario completed + documentation/reflection submitted</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Activity-completion timestamps, KC attempt record, scenario branch log, submitted simulated artifact, time-in-unit log</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>HIGH PHI emphasis (charting); document observations not diagnoses</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Death and Dying: Grief, Comfort, Hospice Awareness, and Postmortem Care Boundaries</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>Death and Dying</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>180</v>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>ContentV2/survey-evidence/_source_text/module-16.txt</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>All lessons viewed + knowledge check attempted + scenario completed + documentation exercise submitted</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>Activity-completion timestamps, KC attempt record, scenario branch log, submitted simulated artifact, time-in-module log</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>Add sensitivity note; confirm postmortem steps; no pronouncement of death</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>All lessons viewed + knowledge check attempted + scenario completed + documentation/reflection submitted</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Activity-completion timestamps, KC attempt record, scenario branch log, submitted simulated artifact, time-in-unit log</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>Add sensitivity note; postmortem-care boundaries; no pronouncement of death</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Patient/Resident Abuse I: Rights, Abuse Types, Prevention, and Risk Recognition</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>Patient/Resident Abuse</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>180</v>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>ContentV2/survey-evidence/_source_text/module-17.txt</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>All lessons viewed + knowledge check attempted + scenario completed + documentation exercise submitted</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>Activity-completion timestamps, KC attempt record, scenario branch log, submitted simulated artifact, time-in-module log</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>All lessons viewed + knowledge check attempted + scenario completed + documentation/reflection submitted</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>Activity-completion timestamps, KC attempt record, scenario branch log, submitted simulated artifact, time-in-unit log</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>Confirm abuse types and resident-rights framing</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Patient/Resident Abuse II: Mandated Reporting, Confidentiality, Documentation, and Final Applied Scenario</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Patient/Resident Abuse</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>ContentV2/survey-evidence/_source_text/module-17.txt</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>All lessons viewed + knowledge check attempted + scenario completed + documentation/reflection submitted</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Activity-completion timestamps, KC attempt record, scenario branch log, submitted simulated artifact, time-in-unit log</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>HIGH: confirm CA mandated-reporter channels/timelines/ombudsman framing</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr"/>
-      <c r="B13" s="4" t="inlineStr"/>
-      <c r="C13" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="B17" s="4" t="inlineStr"/>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>12 units x 2 online CE hours</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="E13" s="4" t="n">
-        <v>1440</v>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>8 modules x 3 online CE hours = 24 (Year1=12, Year2=12)</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>10-17</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Modules 10-17 (source backbone)</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Year 1 = U01-U06 (12h); Year 2 = U07-U12 (12h)</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>Both Year assessments passed at 80% + attestation + seat-time</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>Course completion report + certificate record (post-approval)</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>Master-packet structure conflict (12-Unit vs Modules 10-17): confirm</t>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>Aligned 12-unit x 2-hour structure; no unit-vs-module conflict</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -900,352 +1157,558 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Module_Source_Map - CCCCO NA Model Curriculum (Rev. Dec 2018)</t>
+          <t>Module_Source_Map - each unit mapped to source Modules 10-17</t>
         </is>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>DRAFT / PENDING APPROVAL - Do not advertise, issue certificates, or represent this course as approved until approval status, provider/course identifiers, and certificate wording are confirmed. Online CE only; not clinical hours. Fictional data only; no PHI.</t>
+          <t>DRAFT / PENDING APPROVAL - Do not advertise, issue certificates, or represent this course as approved until approval status, provider/course identifiers, and certificate wording are confirmed. Online CE only; no clinical hours. 12 units x 2 online CE hours = 24. Source backbone: Modules 10-17. Fictional data only; no PHI.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>Unit ID</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Unit Title</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
           <t>Source Module #</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Source Module Title</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Source Topic</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Required Content to Preserve</t>
-        </is>
-      </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>Required Source Content to Preserve</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>LMS Destination</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Assessment Linkage</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Notes / Risks</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>U01</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Vital Signs I: Purpose, Terminology, Temperature, and Pain Observation</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Vital Signs</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>How/when/why vitals taken; T/P/R/BP; recognize &amp; report normal/abnormal; pain; record vitals</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>TPR + BP concepts, adult normal ranges, factors raising/lowering each vital, pain as observation, scope-safe reporting &amp; charting</t>
-        </is>
-      </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Y1 &gt; M10</t>
+          <t>TPR + BP concepts, adult normal ranges, factors raising/lowering vitals, pain as observation, scope-safe reporting/charting</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>KC-M10 + S-M10 + Year 1 Assessment</t>
+          <t>Year 1 &gt; U01</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Keep at observe/report level; no hands-on measurement competency claimed</t>
+          <t>KC-U01 + S-U01 + Year 1 Assessment</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Source title preserved as backbone; objectives at observe/report level</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>U02</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Vital Signs II: Pulse, Respirations, Blood Pressure, Recording, and Reporting</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Vital Signs</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>TPR + BP concepts, adult normal ranges, factors raising/lowering vitals, pain as observation, scope-safe reporting/charting</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Year 1 &gt; U02</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>KC-U02 + S-U02 + Year 1 Assessment</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Source title preserved as backbone; objectives at observe/report level</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>U03</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Nutrition, Hydration, Diets, Feeding Assistance, and Aspiration Awareness</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Nutrition</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Body need for food/fluids; nutrients; therapeutic diets; feeding; hydration; cultural/religious</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Nutrients/food groups, common therapeutic diets, dysphagia/aspiration awareness, hydration/I&amp;O, feeding assistance, cultural respect, alternative routes (observe/report)</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Y1 &gt; M11</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>KC-M11 + S-M11 + Year 1 Assessment</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Feeding stays at assistance level; alternative nutrition routes are observe/report only</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Nutrients/diets, dysphagia/aspiration awareness, hydration/I&amp;O, feeding assistance, cultural respect, alternative routes (observe/report)</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Year 1 &gt; U03</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>KC-U03 + S-U03 + Year 1 Assessment</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Source title preserved as backbone; objectives at observe/report level</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>U04</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Emergency Procedures, Distress Recognition, Choking Response, and Facility Codes</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Emergency Procedures</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Signs/symptoms of distress; CNA immediate/temporary response; choking; emergency codes</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Recognize distress, activate help/EMS chain, choking response within scope, facility codes, scope boundaries</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Y1 &gt; M12</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>KC-M12 + S-M12 + Year 1 Assessment</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>HIGH RISK: explicitly NOT a hands-on CPR/first-aid certification</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Distress recognition, EMS/help chain, conscious-choking response within scope, facility codes, scope boundaries</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Year 1 &gt; U04</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>KC-U04 + S-U04 + Year 1 Assessment</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Source title preserved as backbone; objectives at observe/report level</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>U05</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Long Term Care Patient/Resident I: Aging, Body Systems, and Common Conditions</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Long Term Care Patient/Resident</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Aging effects; common conditions; dementia care; community resources; basic A&amp;P</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Human needs of elderly, dementia-sensitive approaches, special-needs populations, body systems overview, immobility complications</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Y1 &gt; M13</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>KC-M13 + S-M13 + Year 1 Assessment</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Source hours vary (5 SNF/ICF or 3 non-SNF/ICF + 2) - confirm variant</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Aging changes/body systems, common conditions, immobility complications, dementia-sensitive care, psychosocial needs, community resources</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Year 1 &gt; U05</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>KC-U05 + S-U05 + Year 1 Assessment</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Source title preserved as backbone; objectives at observe/report level</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>U06</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Long Term Care Patient/Resident II: Dementia-Sensitive Care, Psychosocial Needs, and Community Resources</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Long Term Care Patient/Resident</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Aging changes/body systems, common conditions, immobility complications, dementia-sensitive care, psychosocial needs, community resources</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Year 1 &gt; U06</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>KC-U06 + S-U06 + Year 1 Assessment</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Source title preserved as backbone; objectives at observe/report level</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>U07</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Rehabilitative Nursing and Restorative Care</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Rehabilitative Nursing</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Restorative care; independence; rehab team; ADLs; ROM; adaptive devices; immobility prevention</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Restorative philosophy, CNA role on rehab team, ADLs, ROM types, adaptive/comfort devices, immobility prevention, documentation/care-plan role</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Y2 &gt; M14</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>KC-M14 + S-M14 + Year 2 Assessment</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>ROM at assist/observe level; no independent therapy claim</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Restorative philosophy, rehab-team role, ADLs, ROM types, adaptive/comfort devices, immobility prevention, documentation role</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Year 2 &gt; U07</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>KC-U07 + S-U07 + Year 2 Assessment</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Source title preserved as backbone; objectives at observe/report level</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>U08</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Observation and Charting I: Objective/Subjective Observation, Terminology, and Reporting Cues</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Observation and Charting</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Objective/subjective observation; medical terminology/abbreviations; charting docs; MDS/ADL</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Senses used in observation, objective vs subjective, charting document types, accurate/timely/factual recording, incident reporting, scope-safe documentation</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Y2 &gt; M15</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>KC-M15 + S-M15 + Year 2 Assessment</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>HIGH PHI emphasis; CNAs document observations not diagnoses</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Objective vs subjective, word elements/abbreviations, charting document types, accurate/timely/factual recording, incident reporting</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Year 2 &gt; U08</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>KC-U08 + S-U08 + Year 2 Assessment</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Source title preserved as backbone; objectives at observe/report level</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>U09</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Observation and Charting II: Charting Documents, Legal Documentation, and Change Reporting</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Observation and Charting</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Objective vs subjective, word elements/abbreviations, charting document types, accurate/timely/factual recording, incident reporting</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Year 2 &gt; U09</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>KC-U09 + S-U09 + Year 2 Assessment</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Source title preserved as backbone; objectives at observe/report level</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Death and Dying: Grief, Comfort, Hospice Awareness, and Postmortem Care Boundaries</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Death and Dying</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Grief stages (Kubler-Ross); emotional/spiritual needs; dying rights; signs of death; hospice; postmortem</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Five stages of grief, comfort/dignity measures, dying rights, approaching vs biological death, hospice role, postmortem responsibilities</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Y2 &gt; M16</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>KC-M16 + S-M16 + Year 2 Assessment</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>Add learner sensitivity/content note; no pronouncement of death</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Five stages of grief, comfort/dignity, dying rights, approaching vs biological death, hospice role, postmortem boundaries</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Year 2 &gt; U10</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>KC-U10 + S-U10 + Year 2 Assessment</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Source title preserved as backbone; objectives at observe/report level</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Patient/Resident Abuse I: Rights, Abuse Types, Prevention, and Risk Recognition</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Patient/Resident Abuse</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Types of abuse; issues; CNA prevention role; CNA reporting role</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Abuse types/definitions, mandated-reporter duty, prevention, recognition, reporting pathways (ombudsman/supervisor/state), confidentiality/HIPAA basics</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Y2 &gt; M17</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>KC-M17 + S-M17 + Year 2 Assessment</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>HIGH: verify current CA mandated-reporter channels and timelines</t>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Abuse types/definitions, mandated-reporter duty, prevention, recognition, reporting pathways, confidentiality/HIPAA basics</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Year 2 &gt; U11</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>KC-U11 + S-U11 + Year 2 Assessment</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Source title preserved as backbone; objectives at observe/report level</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Patient/Resident Abuse II: Mandated Reporting, Confidentiality, Documentation, and Final Applied Scenario</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Patient/Resident Abuse</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Abuse types/definitions, mandated-reporter duty, prevention, recognition, reporting pathways, confidentiality/HIPAA basics</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Year 2 &gt; U12</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>KC-U12 + S-U12 + Year 2 Assessment</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Source title preserved as backbone; objectives at observe/report level</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A2:H2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1257,32 +1720,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:K82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LMS_Activity_Map - Moodle build (Draft)</t>
+          <t>LMS_Activity_Map - Moodle build, unit IDs U01-U12 (Draft)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>DRAFT / PENDING APPROVAL - Do not advertise, issue certificates, or represent this course as approved until approval status, provider/course identifiers, and certificate wording are confirmed. Online CE only; not clinical hours. Fictional data only; no PHI.</t>
+          <t>DRAFT / PENDING APPROVAL - Do not advertise, issue certificates, or represent this course as approved until approval status, provider/course identifiers, and certificate wording are confirmed. Online CE only; no clinical hours. 12 units x 2 online CE hours = 24. Source backbone: Modules 10-17. Fictional data only; no PHI.</t>
         </is>
       </c>
     </row>
@@ -1299,40 +1763,45 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Unit ID</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Source Module #</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Activity Name</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Moodle Activity Type</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Learner Action Required</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Completion Tracking Setting</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Restrict Access Rule</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Gradebook Category</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Evidence Generated</t>
         </is>
@@ -1341,46 +1810,51 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>M10-PAGE</t>
+          <t>U01-PAGE</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>U01</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>M10 Objectives &amp; Banner</t>
-        </is>
-      </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
+          <t>U01 Objectives &amp; Banner</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
           <t>Page</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>View objectives and compliance banner</t>
-        </is>
-      </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
+          <t>View objectives + compliance banner</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>Mark as viewed</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Available after Section 0 complete</t>
-        </is>
-      </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
+          <t>After Section 0 complete</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
           <t>Year 1 - Formative</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>View timestamp</t>
         </is>
@@ -1389,46 +1863,51 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>M10-LSN</t>
+          <t>U01-LSN</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>U01</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>M10 Lesson</t>
-        </is>
-      </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
+          <t>U01 Lesson</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
           <t>Lesson</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Work through branching lesson content</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>Require view (+min pages/time)</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>After M10-PAGE viewed</t>
-        </is>
-      </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
+          <t>After U01-PAGE viewed</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
           <t>Year 1 - Formative</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>Lesson completion + time</t>
         </is>
@@ -1437,46 +1916,51 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>M10-H5P</t>
+          <t>U01-H5P</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>U01</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>M10 Interactive Practice</t>
-        </is>
-      </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
+          <t>U01 Interactive Practice</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
           <t>H5P</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Complete interactive practice</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>Require attempt</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>After M10-LSN viewed</t>
-        </is>
-      </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
+          <t>After U01-LSN viewed</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
           <t>Year 1 - Formative</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>Interaction/xAPI record</t>
         </is>
@@ -1485,46 +1969,51 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>S-M10</t>
+          <t>S-U01</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>U01</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>M10 Scenario (fictional)</t>
-        </is>
-      </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
+          <t>U01 Scenario (fictional)</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
           <t>Lesson (branching)</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Make scope-safe decisions</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Require completion</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>After M10-LSN viewed</t>
-        </is>
-      </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
+          <t>After U01-LSN viewed</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
           <t>Year 1 - Formative</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>Scenario branch log</t>
         </is>
@@ -1533,46 +2022,51 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>KC-M10</t>
+          <t>KC-U01</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>U01</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>M10 Knowledge Check</t>
-        </is>
-      </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
+          <t>U01 Knowledge Check</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
           <t>Quiz</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Attempt low-stakes quiz (unlimited)</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>Require attempt</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>After S-M10 complete</t>
-        </is>
-      </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
+          <t>After S-U01 complete</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
           <t>Year 1 - Formative</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>Attempt record + score</t>
         </is>
@@ -1581,46 +2075,51 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>DOC-M10</t>
+          <t>DOC-U01</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>U01</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>M10 Documentation Exercise</t>
-        </is>
-      </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
+          <t>U01 Documentation/Reflection</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
           <t>Assignment</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>Submit simulated documentation (fictional)</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>Require submission</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>Available with M10-LSN</t>
-        </is>
-      </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
+          <t>Available with U01-LSN</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
           <t>Year 1 - Formative</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>Submitted artifact</t>
         </is>
@@ -1629,46 +2128,51 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>M11-PAGE</t>
+          <t>U02-PAGE</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>M11 Objectives &amp; Banner</t>
-        </is>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>U02</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>10</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
+          <t>U02 Objectives &amp; Banner</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
           <t>Page</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>View objectives and compliance banner</t>
-        </is>
-      </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
+          <t>View objectives + compliance banner</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>Mark as viewed</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>Available after Section 0 complete</t>
-        </is>
-      </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
+          <t>After Section 0 complete</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
           <t>Year 1 - Formative</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>View timestamp</t>
         </is>
@@ -1677,46 +2181,51 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>M11-LSN</t>
+          <t>U02-LSN</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>M11 Lesson</t>
-        </is>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>U02</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>10</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
+          <t>U02 Lesson</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
           <t>Lesson</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>Work through branching lesson content</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>Require view (+min pages/time)</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>After M11-PAGE viewed</t>
-        </is>
-      </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
+          <t>After U02-PAGE viewed</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
           <t>Year 1 - Formative</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>Lesson completion + time</t>
         </is>
@@ -1725,46 +2234,51 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>M11-H5P</t>
+          <t>U02-H5P</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>M11 Interactive Practice</t>
-        </is>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>U02</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>10</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
+          <t>U02 Interactive Practice</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
           <t>H5P</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>Complete interactive practice</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>Require attempt</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>After M11-LSN viewed</t>
-        </is>
-      </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
+          <t>After U02-LSN viewed</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
           <t>Year 1 - Formative</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>Interaction/xAPI record</t>
         </is>
@@ -1773,46 +2287,51 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>S-M11</t>
+          <t>S-U02</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>M11 Scenario (fictional)</t>
-        </is>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>U02</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>10</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
+          <t>U02 Scenario (fictional)</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
           <t>Lesson (branching)</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>Make scope-safe decisions</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>Require completion</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>After M11-LSN viewed</t>
-        </is>
-      </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
+          <t>After U02-LSN viewed</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
           <t>Year 1 - Formative</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>Scenario branch log</t>
         </is>
@@ -1821,46 +2340,51 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>KC-M11</t>
+          <t>KC-U02</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>M11 Knowledge Check</t>
-        </is>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>U02</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>10</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
+          <t>U02 Knowledge Check</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
           <t>Quiz</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>Attempt low-stakes quiz (unlimited)</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>Require attempt</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>After S-M11 complete</t>
-        </is>
-      </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
+          <t>After S-U02 complete</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
           <t>Year 1 - Formative</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>Attempt record + score</t>
         </is>
@@ -1869,46 +2393,51 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>DOC-M11</t>
+          <t>DOC-U02</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C16" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>M11 Documentation Exercise</t>
-        </is>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>U02</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>10</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
+          <t>U02 Documentation/Reflection</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
           <t>Assignment</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>Submit simulated documentation (fictional)</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>Require submission</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>Available with M11-LSN</t>
-        </is>
-      </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
+          <t>Available with U02-LSN</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
           <t>Year 1 - Formative</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>Submitted artifact</t>
         </is>
@@ -1917,46 +2446,51 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>M12-PAGE</t>
+          <t>U03-PAGE</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>M12 Objectives &amp; Banner</t>
-        </is>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>U03</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>11</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
+          <t>U03 Objectives &amp; Banner</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
           <t>Page</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>View objectives and compliance banner</t>
-        </is>
-      </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
+          <t>View objectives + compliance banner</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
           <t>Mark as viewed</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>Available after Section 0 complete</t>
-        </is>
-      </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
+          <t>After Section 0 complete</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
           <t>Year 1 - Formative</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>View timestamp</t>
         </is>
@@ -1965,46 +2499,51 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>M12-LSN</t>
+          <t>U03-LSN</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>M12 Lesson</t>
-        </is>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>U03</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>11</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
+          <t>U03 Lesson</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
           <t>Lesson</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>Work through branching lesson content</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>Require view (+min pages/time)</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>After M12-PAGE viewed</t>
-        </is>
-      </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
+          <t>After U03-PAGE viewed</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
           <t>Year 1 - Formative</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>Lesson completion + time</t>
         </is>
@@ -2013,46 +2552,51 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>M12-H5P</t>
+          <t>U03-H5P</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>M12 Interactive Practice</t>
-        </is>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>U03</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>11</v>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
+          <t>U03 Interactive Practice</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
           <t>H5P</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Complete interactive practice</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>Require attempt</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>After M12-LSN viewed</t>
-        </is>
-      </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
+          <t>After U03-LSN viewed</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
           <t>Year 1 - Formative</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Interaction/xAPI record</t>
         </is>
@@ -2061,46 +2605,51 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>S-M12</t>
+          <t>S-U03</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>M12 Scenario (fictional)</t>
-        </is>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>U03</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>11</v>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
+          <t>U03 Scenario (fictional)</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
           <t>Lesson (branching)</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Make scope-safe decisions</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>Require completion</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>After M12-LSN viewed</t>
-        </is>
-      </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
+          <t>After U03-LSN viewed</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
           <t>Year 1 - Formative</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>Scenario branch log</t>
         </is>
@@ -2109,46 +2658,51 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>KC-M12</t>
+          <t>KC-U03</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C21" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>M12 Knowledge Check</t>
-        </is>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>U03</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>11</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
+          <t>U03 Knowledge Check</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
           <t>Quiz</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>Attempt low-stakes quiz (unlimited)</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>Require attempt</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>After S-M12 complete</t>
-        </is>
-      </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
+          <t>After S-U03 complete</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
           <t>Year 1 - Formative</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>Attempt record + score</t>
         </is>
@@ -2157,46 +2711,51 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>DOC-M12</t>
+          <t>DOC-U03</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>M12 Documentation Exercise</t>
-        </is>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>U03</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>11</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
+          <t>U03 Documentation/Reflection</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
           <t>Assignment</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>Submit simulated documentation (fictional)</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>Require submission</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>Available with M12-LSN</t>
-        </is>
-      </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
+          <t>Available with U03-LSN</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
           <t>Year 1 - Formative</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>Submitted artifact</t>
         </is>
@@ -2205,46 +2764,51 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>M13-PAGE</t>
+          <t>U04-PAGE</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>M13 Objectives &amp; Banner</t>
-        </is>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>U04</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>12</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
+          <t>U04 Objectives &amp; Banner</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
           <t>Page</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>View objectives and compliance banner</t>
-        </is>
-      </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
+          <t>View objectives + compliance banner</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
           <t>Mark as viewed</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Available after Section 0 complete</t>
-        </is>
-      </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
+          <t>After Section 0 complete</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
           <t>Year 1 - Formative</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>View timestamp</t>
         </is>
@@ -2253,46 +2817,51 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>M13-LSN</t>
+          <t>U04-LSN</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C24" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>M13 Lesson</t>
-        </is>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>U04</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>12</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
+          <t>U04 Lesson</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
           <t>Lesson</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>Work through branching lesson content</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>Require view (+min pages/time)</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>After M13-PAGE viewed</t>
-        </is>
-      </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
+          <t>After U04-PAGE viewed</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
           <t>Year 1 - Formative</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>Lesson completion + time</t>
         </is>
@@ -2301,46 +2870,51 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>M13-H5P</t>
+          <t>U04-H5P</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C25" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>M13 Interactive Practice</t>
-        </is>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>U04</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>12</v>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
+          <t>U04 Interactive Practice</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
           <t>H5P</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>Complete interactive practice</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>Require attempt</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>After M13-LSN viewed</t>
-        </is>
-      </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
+          <t>After U04-LSN viewed</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
           <t>Year 1 - Formative</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>Interaction/xAPI record</t>
         </is>
@@ -2349,46 +2923,51 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>S-M13</t>
+          <t>S-U04</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C26" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>M13 Scenario (fictional)</t>
-        </is>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>U04</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>12</v>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
+          <t>U04 Scenario (fictional)</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
           <t>Lesson (branching)</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>Make scope-safe decisions</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>Require completion</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>After M13-LSN viewed</t>
-        </is>
-      </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
+          <t>After U04-LSN viewed</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
           <t>Year 1 - Formative</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>Scenario branch log</t>
         </is>
@@ -2397,46 +2976,51 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>KC-M13</t>
+          <t>KC-U04</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C27" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>M13 Knowledge Check</t>
-        </is>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>U04</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>12</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
+          <t>U04 Knowledge Check</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
           <t>Quiz</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>Attempt low-stakes quiz (unlimited)</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>Require attempt</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>After S-M13 complete</t>
-        </is>
-      </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
+          <t>After S-U04 complete</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
           <t>Year 1 - Formative</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>Attempt record + score</t>
         </is>
@@ -2445,46 +3029,51 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>DOC-M13</t>
+          <t>DOC-U04</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C28" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>M13 Documentation Exercise</t>
-        </is>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>U04</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>12</v>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
+          <t>U04 Documentation/Reflection</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
           <t>Assignment</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>Submit simulated documentation (fictional)</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>Require submission</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>Available with M13-LSN</t>
-        </is>
-      </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
+          <t>Available with U04-LSN</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
           <t>Year 1 - Formative</t>
         </is>
       </c>
-      <c r="J28" s="4" t="inlineStr">
+      <c r="K28" s="4" t="inlineStr">
         <is>
           <t>Submitted artifact</t>
         </is>
@@ -2493,46 +3082,51 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>M14-PAGE</t>
+          <t>U05-PAGE</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>M14 Objectives &amp; Banner</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>U05</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>13</v>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
+          <t>U05 Objectives &amp; Banner</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
           <t>Page</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>View objectives and compliance banner</t>
-        </is>
-      </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
+          <t>View objectives + compliance banner</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
           <t>Mark as viewed</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>Available after Section 0 complete</t>
-        </is>
-      </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Year 2 - Formative</t>
+          <t>After Section 0 complete</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>Year 1 - Formative</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
         <is>
           <t>View timestamp</t>
         </is>
@@ -2541,46 +3135,51 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>M14-LSN</t>
+          <t>U05-LSN</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>M14 Lesson</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>U05</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>13</v>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
+          <t>U05 Lesson</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
           <t>Lesson</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>Work through branching lesson content</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>Require view (+min pages/time)</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>After M14-PAGE viewed</t>
-        </is>
-      </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Year 2 - Formative</t>
+          <t>After U05-PAGE viewed</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>Year 1 - Formative</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
         <is>
           <t>Lesson completion + time</t>
         </is>
@@ -2589,46 +3188,51 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>M14-H5P</t>
+          <t>U05-H5P</t>
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>M14 Interactive Practice</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>U05</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>13</v>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
+          <t>U05 Interactive Practice</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
           <t>H5P</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>Complete interactive practice</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>Require attempt</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>After M14-LSN viewed</t>
-        </is>
-      </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Year 2 - Formative</t>
+          <t>After U05-LSN viewed</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>Year 1 - Formative</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
         <is>
           <t>Interaction/xAPI record</t>
         </is>
@@ -2637,46 +3241,51 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>S-M14</t>
+          <t>S-U05</t>
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>M14 Scenario (fictional)</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>U05</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>13</v>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
+          <t>U05 Scenario (fictional)</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
           <t>Lesson (branching)</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>Make scope-safe decisions</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>Require completion</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>After M14-LSN viewed</t>
-        </is>
-      </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Year 2 - Formative</t>
+          <t>After U05-LSN viewed</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>Year 1 - Formative</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
         <is>
           <t>Scenario branch log</t>
         </is>
@@ -2685,46 +3294,51 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>KC-M14</t>
+          <t>KC-U05</t>
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>M14 Knowledge Check</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>U05</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>13</v>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
+          <t>U05 Knowledge Check</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
           <t>Quiz</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>Attempt low-stakes quiz (unlimited)</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t>Require attempt</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>After S-M14 complete</t>
-        </is>
-      </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Year 2 - Formative</t>
+          <t>After S-U05 complete</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>Year 1 - Formative</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
         <is>
           <t>Attempt record + score</t>
         </is>
@@ -2733,46 +3347,51 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>DOC-M14</t>
+          <t>DOC-U05</t>
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>M14 Documentation Exercise</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>U05</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>13</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
+          <t>U05 Documentation/Reflection</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
           <t>Assignment</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>Submit simulated documentation (fictional)</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>Require submission</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>Available with M14-LSN</t>
-        </is>
-      </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Year 2 - Formative</t>
+          <t>Available with U05-LSN</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>Year 1 - Formative</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
         <is>
           <t>Submitted artifact</t>
         </is>
@@ -2781,46 +3400,51 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>M15-PAGE</t>
+          <t>U06-PAGE</t>
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>M15 Objectives &amp; Banner</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>U06</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>13</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
+          <t>U06 Objectives &amp; Banner</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
           <t>Page</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>View objectives and compliance banner</t>
-        </is>
-      </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
+          <t>View objectives + compliance banner</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
           <t>Mark as viewed</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>Available after Section 0 complete</t>
-        </is>
-      </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Year 2 - Formative</t>
+          <t>After Section 0 complete</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>Year 1 - Formative</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
         <is>
           <t>View timestamp</t>
         </is>
@@ -2829,46 +3453,51 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>M15-LSN</t>
+          <t>U06-LSN</t>
         </is>
       </c>
       <c r="B36" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>M15 Lesson</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>U06</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>13</v>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
+          <t>U06 Lesson</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
           <t>Lesson</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>Work through branching lesson content</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr">
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>Require view (+min pages/time)</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>After M15-PAGE viewed</t>
-        </is>
-      </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Year 2 - Formative</t>
+          <t>After U06-PAGE viewed</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>Year 1 - Formative</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
         <is>
           <t>Lesson completion + time</t>
         </is>
@@ -2877,46 +3506,51 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>M15-H5P</t>
+          <t>U06-H5P</t>
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>M15 Interactive Practice</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>U06</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>13</v>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
+          <t>U06 Interactive Practice</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
           <t>H5P</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>Complete interactive practice</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="H37" s="4" t="inlineStr">
         <is>
           <t>Require attempt</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>After M15-LSN viewed</t>
-        </is>
-      </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Year 2 - Formative</t>
+          <t>After U06-LSN viewed</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>Year 1 - Formative</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
         <is>
           <t>Interaction/xAPI record</t>
         </is>
@@ -2925,46 +3559,51 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>S-M15</t>
+          <t>S-U06</t>
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>M15 Scenario (fictional)</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>U06</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>13</v>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
+          <t>U06 Scenario (fictional)</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
           <t>Lesson (branching)</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>Make scope-safe decisions</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
         <is>
           <t>Require completion</t>
         </is>
       </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>After M15-LSN viewed</t>
-        </is>
-      </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Year 2 - Formative</t>
+          <t>After U06-LSN viewed</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>Year 1 - Formative</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
         <is>
           <t>Scenario branch log</t>
         </is>
@@ -2973,46 +3612,51 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>KC-M15</t>
+          <t>KC-U06</t>
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>M15 Knowledge Check</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>U06</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>13</v>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
+          <t>U06 Knowledge Check</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
           <t>Quiz</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>Attempt low-stakes quiz (unlimited)</t>
         </is>
       </c>
-      <c r="G39" s="4" t="inlineStr">
+      <c r="H39" s="4" t="inlineStr">
         <is>
           <t>Require attempt</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>After S-M15 complete</t>
-        </is>
-      </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Year 2 - Formative</t>
+          <t>After S-U06 complete</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>Year 1 - Formative</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
         <is>
           <t>Attempt record + score</t>
         </is>
@@ -3021,46 +3665,51 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>DOC-M15</t>
+          <t>DOC-U06</t>
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>M15 Documentation Exercise</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>U06</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>13</v>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
+          <t>U06 Documentation/Reflection</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
           <t>Assignment</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>Submit simulated documentation (fictional)</t>
         </is>
       </c>
-      <c r="G40" s="4" t="inlineStr">
+      <c r="H40" s="4" t="inlineStr">
         <is>
           <t>Require submission</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>Available with M15-LSN</t>
-        </is>
-      </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Year 2 - Formative</t>
+          <t>Available with U06-LSN</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>Year 1 - Formative</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
         <is>
           <t>Submitted artifact</t>
         </is>
@@ -3069,46 +3718,51 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>M16-PAGE</t>
+          <t>U07-PAGE</t>
         </is>
       </c>
       <c r="B41" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C41" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>M16 Objectives &amp; Banner</t>
-        </is>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>U07</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>14</v>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
+          <t>U07 Objectives &amp; Banner</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
           <t>Page</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>View objectives and compliance banner</t>
-        </is>
-      </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
+          <t>View objectives + compliance banner</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
           <t>Mark as viewed</t>
         </is>
       </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>Available after Section 0 complete</t>
-        </is>
-      </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
+          <t>After Section 0 complete</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
           <t>Year 2 - Formative</t>
         </is>
       </c>
-      <c r="J41" s="4" t="inlineStr">
+      <c r="K41" s="4" t="inlineStr">
         <is>
           <t>View timestamp</t>
         </is>
@@ -3117,46 +3771,51 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>M16-LSN</t>
+          <t>U07-LSN</t>
         </is>
       </c>
       <c r="B42" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C42" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>M16 Lesson</t>
-        </is>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>U07</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>14</v>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
+          <t>U07 Lesson</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
           <t>Lesson</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="G42" s="4" t="inlineStr">
         <is>
           <t>Work through branching lesson content</t>
         </is>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="H42" s="4" t="inlineStr">
         <is>
           <t>Require view (+min pages/time)</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>After M16-PAGE viewed</t>
-        </is>
-      </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
+          <t>After U07-PAGE viewed</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
           <t>Year 2 - Formative</t>
         </is>
       </c>
-      <c r="J42" s="4" t="inlineStr">
+      <c r="K42" s="4" t="inlineStr">
         <is>
           <t>Lesson completion + time</t>
         </is>
@@ -3165,46 +3824,51 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>M16-H5P</t>
+          <t>U07-H5P</t>
         </is>
       </c>
       <c r="B43" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C43" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>M16 Interactive Practice</t>
-        </is>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>U07</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>14</v>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
+          <t>U07 Interactive Practice</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
           <t>H5P</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="G43" s="4" t="inlineStr">
         <is>
           <t>Complete interactive practice</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="H43" s="4" t="inlineStr">
         <is>
           <t>Require attempt</t>
         </is>
       </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>After M16-LSN viewed</t>
-        </is>
-      </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
+          <t>After U07-LSN viewed</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
           <t>Year 2 - Formative</t>
         </is>
       </c>
-      <c r="J43" s="4" t="inlineStr">
+      <c r="K43" s="4" t="inlineStr">
         <is>
           <t>Interaction/xAPI record</t>
         </is>
@@ -3213,46 +3877,51 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>S-M16</t>
+          <t>S-U07</t>
         </is>
       </c>
       <c r="B44" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C44" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>M16 Scenario (fictional)</t>
-        </is>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>U07</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>14</v>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
+          <t>U07 Scenario (fictional)</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
           <t>Lesson (branching)</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="G44" s="4" t="inlineStr">
         <is>
           <t>Make scope-safe decisions</t>
         </is>
       </c>
-      <c r="G44" s="4" t="inlineStr">
+      <c r="H44" s="4" t="inlineStr">
         <is>
           <t>Require completion</t>
         </is>
       </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>After M16-LSN viewed</t>
-        </is>
-      </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
+          <t>After U07-LSN viewed</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
           <t>Year 2 - Formative</t>
         </is>
       </c>
-      <c r="J44" s="4" t="inlineStr">
+      <c r="K44" s="4" t="inlineStr">
         <is>
           <t>Scenario branch log</t>
         </is>
@@ -3261,46 +3930,51 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>KC-M16</t>
+          <t>KC-U07</t>
         </is>
       </c>
       <c r="B45" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C45" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>M16 Knowledge Check</t>
-        </is>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>U07</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>14</v>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
+          <t>U07 Knowledge Check</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
           <t>Quiz</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="G45" s="4" t="inlineStr">
         <is>
           <t>Attempt low-stakes quiz (unlimited)</t>
         </is>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="H45" s="4" t="inlineStr">
         <is>
           <t>Require attempt</t>
         </is>
       </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>After S-M16 complete</t>
-        </is>
-      </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
+          <t>After S-U07 complete</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
           <t>Year 2 - Formative</t>
         </is>
       </c>
-      <c r="J45" s="4" t="inlineStr">
+      <c r="K45" s="4" t="inlineStr">
         <is>
           <t>Attempt record + score</t>
         </is>
@@ -3309,46 +3983,51 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>DOC-M16</t>
+          <t>DOC-U07</t>
         </is>
       </c>
       <c r="B46" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C46" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>M16 Documentation Exercise</t>
-        </is>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>U07</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>14</v>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
+          <t>U07 Documentation/Reflection</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
           <t>Assignment</t>
         </is>
       </c>
-      <c r="F46" s="4" t="inlineStr">
+      <c r="G46" s="4" t="inlineStr">
         <is>
           <t>Submit simulated documentation (fictional)</t>
         </is>
       </c>
-      <c r="G46" s="4" t="inlineStr">
+      <c r="H46" s="4" t="inlineStr">
         <is>
           <t>Require submission</t>
         </is>
       </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>Available with M16-LSN</t>
-        </is>
-      </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
+          <t>Available with U07-LSN</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
           <t>Year 2 - Formative</t>
         </is>
       </c>
-      <c r="J46" s="4" t="inlineStr">
+      <c r="K46" s="4" t="inlineStr">
         <is>
           <t>Submitted artifact</t>
         </is>
@@ -3357,46 +4036,51 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>M17-PAGE</t>
+          <t>U08-PAGE</t>
         </is>
       </c>
       <c r="B47" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C47" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>M17 Objectives &amp; Banner</t>
-        </is>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>U08</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>15</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
+          <t>U08 Objectives &amp; Banner</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
           <t>Page</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>View objectives and compliance banner</t>
-        </is>
-      </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
+          <t>View objectives + compliance banner</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
           <t>Mark as viewed</t>
         </is>
       </c>
-      <c r="H47" s="4" t="inlineStr">
-        <is>
-          <t>Available after Section 0 complete</t>
-        </is>
-      </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
+          <t>After Section 0 complete</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
           <t>Year 2 - Formative</t>
         </is>
       </c>
-      <c r="J47" s="4" t="inlineStr">
+      <c r="K47" s="4" t="inlineStr">
         <is>
           <t>View timestamp</t>
         </is>
@@ -3405,46 +4089,51 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>M17-LSN</t>
+          <t>U08-LSN</t>
         </is>
       </c>
       <c r="B48" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C48" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>M17 Lesson</t>
-        </is>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>U08</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>15</v>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
+          <t>U08 Lesson</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
           <t>Lesson</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="G48" s="4" t="inlineStr">
         <is>
           <t>Work through branching lesson content</t>
         </is>
       </c>
-      <c r="G48" s="4" t="inlineStr">
+      <c r="H48" s="4" t="inlineStr">
         <is>
           <t>Require view (+min pages/time)</t>
         </is>
       </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>After M17-PAGE viewed</t>
-        </is>
-      </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
+          <t>After U08-PAGE viewed</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
           <t>Year 2 - Formative</t>
         </is>
       </c>
-      <c r="J48" s="4" t="inlineStr">
+      <c r="K48" s="4" t="inlineStr">
         <is>
           <t>Lesson completion + time</t>
         </is>
@@ -3453,46 +4142,51 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>M17-H5P</t>
+          <t>U08-H5P</t>
         </is>
       </c>
       <c r="B49" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C49" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>M17 Interactive Practice</t>
-        </is>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>U08</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>15</v>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
+          <t>U08 Interactive Practice</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
           <t>H5P</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="G49" s="4" t="inlineStr">
         <is>
           <t>Complete interactive practice</t>
         </is>
       </c>
-      <c r="G49" s="4" t="inlineStr">
+      <c r="H49" s="4" t="inlineStr">
         <is>
           <t>Require attempt</t>
         </is>
       </c>
-      <c r="H49" s="4" t="inlineStr">
-        <is>
-          <t>After M17-LSN viewed</t>
-        </is>
-      </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
+          <t>After U08-LSN viewed</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
           <t>Year 2 - Formative</t>
         </is>
       </c>
-      <c r="J49" s="4" t="inlineStr">
+      <c r="K49" s="4" t="inlineStr">
         <is>
           <t>Interaction/xAPI record</t>
         </is>
@@ -3501,46 +4195,51 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>S-M17</t>
+          <t>S-U08</t>
         </is>
       </c>
       <c r="B50" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C50" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>M17 Scenario (fictional)</t>
-        </is>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>U08</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>15</v>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
+          <t>U08 Scenario (fictional)</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
           <t>Lesson (branching)</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="G50" s="4" t="inlineStr">
         <is>
           <t>Make scope-safe decisions</t>
         </is>
       </c>
-      <c r="G50" s="4" t="inlineStr">
+      <c r="H50" s="4" t="inlineStr">
         <is>
           <t>Require completion</t>
         </is>
       </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>After M17-LSN viewed</t>
-        </is>
-      </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
+          <t>After U08-LSN viewed</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
           <t>Year 2 - Formative</t>
         </is>
       </c>
-      <c r="J50" s="4" t="inlineStr">
+      <c r="K50" s="4" t="inlineStr">
         <is>
           <t>Scenario branch log</t>
         </is>
@@ -3549,46 +4248,51 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>KC-M17</t>
+          <t>KC-U08</t>
         </is>
       </c>
       <c r="B51" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C51" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>M17 Knowledge Check</t>
-        </is>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>U08</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>15</v>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
+          <t>U08 Knowledge Check</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
           <t>Quiz</t>
         </is>
       </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="G51" s="4" t="inlineStr">
         <is>
           <t>Attempt low-stakes quiz (unlimited)</t>
         </is>
       </c>
-      <c r="G51" s="4" t="inlineStr">
+      <c r="H51" s="4" t="inlineStr">
         <is>
           <t>Require attempt</t>
         </is>
       </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>After S-M17 complete</t>
-        </is>
-      </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
+          <t>After S-U08 complete</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
           <t>Year 2 - Formative</t>
         </is>
       </c>
-      <c r="J51" s="4" t="inlineStr">
+      <c r="K51" s="4" t="inlineStr">
         <is>
           <t>Attempt record + score</t>
         </is>
@@ -3597,46 +4301,51 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>DOC-M17</t>
+          <t>DOC-U08</t>
         </is>
       </c>
       <c r="B52" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C52" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>M17 Documentation Exercise</t>
-        </is>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>U08</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>15</v>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
+          <t>U08 Documentation/Reflection</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
           <t>Assignment</t>
         </is>
       </c>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="G52" s="4" t="inlineStr">
         <is>
           <t>Submit simulated documentation (fictional)</t>
         </is>
       </c>
-      <c r="G52" s="4" t="inlineStr">
+      <c r="H52" s="4" t="inlineStr">
         <is>
           <t>Require submission</t>
         </is>
       </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>Available with M17-LSN</t>
-        </is>
-      </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
+          <t>Available with U08-LSN</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
           <t>Year 2 - Formative</t>
         </is>
       </c>
-      <c r="J52" s="4" t="inlineStr">
+      <c r="K52" s="4" t="inlineStr">
         <is>
           <t>Submitted artifact</t>
         </is>
@@ -3645,430 +4354,1600 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>SEC0-ID</t>
+          <t>U09-PAGE</t>
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>Identity Confirmation</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>U09</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>15</v>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Feedback/Choice</t>
+          <t>U09 Objectives &amp; Banner</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Confirm legal name (+CNA # if required)</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>Require submission</t>
+          <t>View objectives + compliance banner</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>Available at enrollment</t>
+          <t>Mark as viewed</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>Orientation</t>
+          <t>After Section 0 complete</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>Identity record</t>
+          <t>Year 2 - Formative</t>
+        </is>
+      </c>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>View timestamp</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>SEC0-NOPHI</t>
+          <t>U09-LSN</t>
         </is>
       </c>
       <c r="B54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>No-PHI Agreement</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>U09</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>15</v>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>U09 Lesson</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Accept no-PHI agreement</t>
+          <t>Lesson</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>Require submission</t>
+          <t>Work through branching lesson content</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>Available at enrollment</t>
+          <t>Require view (+min pages/time)</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>Orientation</t>
+          <t>After U09-PAGE viewed</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>Agreement record</t>
+          <t>Year 2 - Formative</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>Lesson completion + time</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Y1-ATTEST</t>
+          <t>U09-H5P</t>
         </is>
       </c>
       <c r="B55" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>Year 1 Integrity Attestation</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>U09</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>15</v>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>U09 Interactive Practice</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Re-attest before Year 1 assessment</t>
+          <t>H5P</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>Require submission</t>
+          <t>Complete interactive practice</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>After M10-M13 complete</t>
+          <t>Require attempt</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>Year 1 - Summative</t>
+          <t>After U09-LSN viewed</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>Attestation record</t>
+          <t>Year 2 - Formative</t>
+        </is>
+      </c>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>Interaction/xAPI record</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Y1-ASSESS</t>
+          <t>S-U09</t>
         </is>
       </c>
       <c r="B56" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>Year 1 Assessment</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>U09</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>15</v>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Quiz</t>
+          <t>U09 Scenario (fictional)</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Pass summative at 80%</t>
+          <t>Lesson (branching)</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>Require pass grade (&gt;=80%)</t>
+          <t>Make scope-safe decisions</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>After M10-M13 complete + Y1-ATTEST</t>
+          <t>Require completion</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>Year 1 - Summative</t>
+          <t>After U09-LSN viewed</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>Attempts, score, duration</t>
+          <t>Year 2 - Formative</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>Scenario branch log</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Y2-ATTEST</t>
+          <t>KC-U09</t>
         </is>
       </c>
       <c r="B57" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>Year 2 Integrity Attestation</t>
-        </is>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>U09</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>15</v>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>U09 Knowledge Check</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Re-attest before Year 2 assessment</t>
+          <t>Quiz</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>Require submission</t>
+          <t>Attempt low-stakes quiz (unlimited)</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>After M14-M17 complete</t>
+          <t>Require attempt</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>Year 2 - Summative</t>
+          <t>After S-U09 complete</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>Attestation record</t>
+          <t>Year 2 - Formative</t>
+        </is>
+      </c>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>Attempt record + score</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Y2-ASSESS</t>
+          <t>DOC-U09</t>
         </is>
       </c>
       <c r="B58" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>Year 2 Assessment</t>
-        </is>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>U09</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>15</v>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Quiz</t>
+          <t>U09 Documentation/Reflection</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Pass summative at 80%</t>
+          <t>Assignment</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>Require pass grade (&gt;=80%)</t>
+          <t>Submit simulated documentation (fictional)</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>After M14-M17 complete + Y2-ATTEST</t>
+          <t>Require submission</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>Year 2 - Summative</t>
+          <t>Available with U09-LSN</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>Attempts, score, duration</t>
+          <t>Year 2 - Formative</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>Submitted artifact</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>FINAL-AFF</t>
+          <t>U10-PAGE</t>
         </is>
       </c>
       <c r="B59" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>Final Affidavit</t>
-        </is>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>16</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Assignment</t>
+          <t>U10 Objectives &amp; Banner</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Submit completion affidavit</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>Require submission</t>
+          <t>View objectives + compliance banner</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>After both Year assessments passed</t>
+          <t>Mark as viewed</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>Course</t>
+          <t>After Section 0 complete</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>Affidavit submission</t>
+          <t>Year 2 - Formative</t>
+        </is>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>View timestamp</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>EVAL</t>
+          <t>U10-LSN</t>
         </is>
       </c>
       <c r="B60" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>Course Evaluation</t>
-        </is>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>16</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>U10 Lesson</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Complete evaluation (no PHI)</t>
+          <t>Lesson</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>Require submission</t>
+          <t>Work through branching lesson content</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>After final affidavit</t>
+          <t>Require view (+min pages/time)</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>Course</t>
+          <t>After U10-PAGE viewed</t>
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>Evaluation responses</t>
+          <t>Year 2 - Formative</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>Lesson completion + time</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>U10-H5P</t>
         </is>
       </c>
       <c r="B61" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C61" s="4" t="n">
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>U10 Interactive Practice</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>H5P</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>Complete interactive practice</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>Require attempt</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>After U10-LSN viewed</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>Year 2 - Formative</t>
+        </is>
+      </c>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>Interaction/xAPI record</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>S-U10</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>U10 Scenario (fictional)</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>Lesson (branching)</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>Make scope-safe decisions</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>Require completion</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>After U10-LSN viewed</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>Year 2 - Formative</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>Scenario branch log</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>KC-U10</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>U10 Knowledge Check</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>Quiz</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>Attempt low-stakes quiz (unlimited)</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>Require attempt</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>After S-U10 complete</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>Year 2 - Formative</t>
+        </is>
+      </c>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>Attempt record + score</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>DOC-U10</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>U10 Documentation/Reflection</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>Assignment</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>Submit simulated documentation (fictional)</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>Require submission</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>Available with U10-LSN</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>Year 2 - Formative</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>Submitted artifact</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>U11-PAGE</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>U11 Objectives &amp; Banner</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>View objectives + compliance banner</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>Mark as viewed</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>After Section 0 complete</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>Year 2 - Formative</t>
+        </is>
+      </c>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>View timestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>U11-LSN</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>U11 Lesson</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>Work through branching lesson content</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>Require view (+min pages/time)</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>After U11-PAGE viewed</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>Year 2 - Formative</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>Lesson completion + time</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>U11-H5P</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>U11 Interactive Practice</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>H5P</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>Complete interactive practice</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>Require attempt</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>After U11-LSN viewed</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>Year 2 - Formative</t>
+        </is>
+      </c>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>Interaction/xAPI record</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>S-U11</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>U11 Scenario (fictional)</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>Lesson (branching)</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>Make scope-safe decisions</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>Require completion</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>After U11-LSN viewed</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>Year 2 - Formative</t>
+        </is>
+      </c>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>Scenario branch log</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>KC-U11</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>U11 Knowledge Check</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>Quiz</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>Attempt low-stakes quiz (unlimited)</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>Require attempt</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>After S-U11 complete</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>Year 2 - Formative</t>
+        </is>
+      </c>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>Attempt record + score</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>DOC-U11</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>U11 Documentation/Reflection</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>Assignment</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>Submit simulated documentation (fictional)</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>Require submission</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>Available with U11-LSN</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>Year 2 - Formative</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>Submitted artifact</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>U12-PAGE</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>U12 Objectives &amp; Banner</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>View objectives + compliance banner</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>Mark as viewed</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>After Section 0 complete</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>Year 2 - Formative</t>
+        </is>
+      </c>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>View timestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>U12-LSN</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>U12 Lesson</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>Work through branching lesson content</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>Require view (+min pages/time)</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>After U12-PAGE viewed</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>Year 2 - Formative</t>
+        </is>
+      </c>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>Lesson completion + time</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>U12-H5P</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>U12 Interactive Practice</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>H5P</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>Complete interactive practice</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>Require attempt</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>After U12-LSN viewed</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>Year 2 - Formative</t>
+        </is>
+      </c>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>Interaction/xAPI record</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>S-U12</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>U12 Scenario (fictional)</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>Lesson (branching)</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>Make scope-safe decisions</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>Require completion</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>After U12-LSN viewed</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>Year 2 - Formative</t>
+        </is>
+      </c>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>Scenario branch log</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>KC-U12</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>U12 Knowledge Check</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>Quiz</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>Attempt low-stakes quiz (unlimited)</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>Require attempt</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>After S-U12 complete</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>Year 2 - Formative</t>
+        </is>
+      </c>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>Attempt record + score</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>DOC-U12</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>U12 Documentation/Reflection</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>Assignment</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>Submit simulated documentation (fictional)</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>Require submission</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>Available with U12-LSN</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>Year 2 - Formative</t>
+        </is>
+      </c>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>Submitted artifact</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>SEC0-ID</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>Identity Confirmation</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>Feedback/Choice</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>Confirm legal name (+CNA # if required)</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>Require submission</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>Available at enrollment</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>Orientation</t>
+        </is>
+      </c>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>Identity record</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>SEC0-NOPHI</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>No-PHI Agreement</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>Feedback</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>Accept no-PHI agreement</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>Require submission</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>Available at enrollment</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>Orientation</t>
+        </is>
+      </c>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>Agreement record</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>Y1-ASSESS</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>10-13</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Year 1 Assessment</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>Quiz</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>Pass summative at 80%</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>Require pass grade (&gt;=80%)</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>After U01-U06 complete</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>Year 1 - Summative</t>
+        </is>
+      </c>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>Attempts, score, duration</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Y2-ASSESS</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>14-17</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>Year 2 Assessment</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>Quiz</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>Pass summative at 80%</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>Require pass grade (&gt;=80%)</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>After U07-U12 complete</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>Year 2 - Summative</t>
+        </is>
+      </c>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>Attempts, score, duration</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>FINAL-AFF</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>Final Affidavit</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>Assignment</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>Submit completion affidavit</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>Require submission</t>
+        </is>
+      </c>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>After both Year assessments passed</t>
+        </is>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>Course</t>
+        </is>
+      </c>
+      <c r="K81" s="4" t="inlineStr">
+        <is>
+          <t>Affidavit submission</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>CERT</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
         <is>
           <t>Certificate (gated, post-approval)</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
+      <c r="F82" s="4" t="inlineStr">
         <is>
           <t>Custom certificate</t>
         </is>
       </c>
-      <c r="F61" s="4" t="inlineStr">
+      <c r="G82" s="4" t="inlineStr">
         <is>
           <t>Download once gate met + approval confirmed</t>
         </is>
       </c>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="H82" s="4" t="inlineStr">
         <is>
           <t>Restricted by course completion</t>
         </is>
       </c>
-      <c r="H61" s="4" t="inlineStr">
+      <c r="I82" s="4" t="inlineStr">
         <is>
           <t>After all gate items incl. APPROVAL CONFIRMED (currently OFF)</t>
         </is>
       </c>
-      <c r="I61" s="4" t="inlineStr">
+      <c r="J82" s="4" t="inlineStr">
         <is>
           <t>Course</t>
         </is>
       </c>
-      <c r="J61" s="4" t="inlineStr">
+      <c r="K82" s="4" t="inlineStr">
         <is>
           <t>Certificate record + unique ID</t>
         </is>
@@ -4076,7 +5955,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:K2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4088,32 +5967,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Assessment_Blueprint - seed items (Internal answer key - DO NOT publish)</t>
+          <t>Assessment_Blueprint - seed items mapped to U01-U12 (Internal key - DO NOT publish)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>DRAFT / PENDING APPROVAL - Do not advertise, issue certificates, or represent this course as approved until approval status, provider/course identifiers, and certificate wording are confirmed. Online CE only; not clinical hours. Fictional data only; no PHI.</t>
+          <t>DRAFT / PENDING APPROVAL - Do not advertise, issue certificates, or represent this course as approved until approval status, provider/course identifiers, and certificate wording are confirmed. Online CE only; no clinical hours. 12 units x 2 online CE hours = 24. Source backbone: Modules 10-17. Fictional data only; no PHI.</t>
         </is>
       </c>
     </row>
@@ -4125,22 +6004,22 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>Unit ID</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
           <t>Source Module #</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Question Type</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Question Stem</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Answer Choices</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -4172,40 +6051,40 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>KC-M10-01</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
+          <t>KC-U01-01</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>U01</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Which adult finding should the CNA report to the licensed nurse as abnormal?</t>
+          <t>MCQ/TF</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>A) Pulse 72  B) Resp 16  C) Pulse 124  D) Oral temp 98.6F</t>
+          <t>Which adult finding should the CNA report to the nurse as abnormal?</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Oral temp 103F (febrile)</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Adult pulse &gt;100 (tachycardia) is abnormal and reported.</t>
+          <t>Febrile temperature is abnormal and reported within scope.</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Review M10 normal ranges and reporting (L10.2-L10.3).</t>
+          <t>Route to U01 lesson review (source Module 10).</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -4215,34 +6094,34 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>Full key</t>
+          <t>Full internal key</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>KC-M10-02</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
+          <t>KC-U02-01</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>U02</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>True/False</t>
-        </is>
-      </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
+          <t>MCQ/TF</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
           <t>A CNA may adjust a resident's blood pressure medication if the reading is high.</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>True / False</t>
-        </is>
-      </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
           <t>False</t>
@@ -4255,7 +6134,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Review M10 scope-of-practice and reporting (L10.5-L10.6).</t>
+          <t>Route to U02 lesson review (source Module 10).</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -4265,47 +6144,47 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>Full key</t>
+          <t>Full internal key</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>KC-M11-01</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
+          <t>KC-U03-01</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>U03</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Matching</t>
-        </is>
-      </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Match the therapeutic diet to its description.</t>
+          <t>MCQ/TF</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Pureed / Clear liquid / Low-sodium / Mechanical soft (descriptions provided)</t>
+          <t>A resident on a thickened-liquid diet is served thin juice. The CNA should:</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Correct pairings per source</t>
+          <t>Withhold and verify the diet order with the nurse</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Diets are ordered; CNA assists and reports intake.</t>
+          <t>Aspiration risk; verify order and report before serving.</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Review M11 therapeutic diets (L11.4).</t>
+          <t>Route to U03 lesson review (source Module 11).</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -4315,47 +6194,47 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>Full key</t>
+          <t>Full internal key</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>KC-M11-02</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
+          <t>KC-U04-01</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>U04</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>12</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>A resident on a thickened-liquid diet is served thin juice. The CNA should:</t>
+          <t>MCQ/TF</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>A) Serve it  B) Withhold and verify the diet order with the nurse  C) Thin it more  D) Ignore</t>
+          <t>Completing this online unit certifies the CNA in hands-on CPR.</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>False</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Aspiration risk; verify order and report before serving.</t>
+          <t>Online CE only; hands-on CPR certification is separate.</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Review M11 aspiration precautions and scope (L11.5).</t>
+          <t>Route to U04 lesson review (source Module 12).</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -4365,47 +6244,47 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>Full key</t>
+          <t>Full internal key</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>KC-M12-01</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
+          <t>KC-U05-01</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>U05</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>13</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>A resident returns from a walk reporting shortness of breath and chest tightness. FIRST CNA action?</t>
+          <t>MCQ/TF</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>A) Reassure they'll be fine  B) Take vitals  C) Stay and call the nurse immediately  D) Call family</t>
+          <t>Which is a complication of immobility the CNA observes and reports?</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Pressure injury / skin breakdown</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Stay with resident and summon the nurse/EMS chain immediately.</t>
+          <t>Immobility raises pressure-injury risk; observe and report.</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Review M12 immediate interventions (L12.2).</t>
+          <t>Route to U05 lesson review (source Module 13).</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -4415,47 +6294,47 @@
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>Full key</t>
+          <t>Full internal key</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>KC-M12-02</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>True/False</t>
-        </is>
+          <t>KC-U06-01</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>U06</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>13</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Completing this online module certifies the CNA in hands-on CPR.</t>
+          <t>MCQ/TF</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>True / False</t>
+          <t>A resident with dementia is agitated during evening care. Best scope-safe approach?</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Calm, simple, reassuring approach; reduce stimulation</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>This is online CE only; hands-on CPR certification is separate.</t>
+          <t>Person-centered de-escalation within scope.</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Review M12 banner and scope note (L12.1).</t>
+          <t>Route to U06 lesson review (source Module 13).</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -4465,47 +6344,47 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>Full key</t>
+          <t>Full internal key</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>KC-M13-01</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
+          <t>KC-U07-01</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>U07</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>14</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>A resident with dementia is agitated during evening care. Best scope-safe approach?</t>
+          <t>MCQ/TF</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>A) Argue with the facts  B) Use a calm, simple, reassuring approach and reduce stimulation  C) Restrain  D) Leave alone</t>
+          <t>Restorative care for a resident who can do part of their ADLs means the CNA should:</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Assist only as needed and encourage independence</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Person-centered, dignity-preserving de-escalation within scope.</t>
+          <t>Restorative philosophy promotes maximum independence.</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Review M13 dementia-sensitive care (L13.3).</t>
+          <t>Route to U07 lesson review (source Module 14).</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -4515,47 +6394,47 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>Full key</t>
+          <t>Full internal key</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>KC-M13-02</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
+          <t>KC-U08-01</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>U08</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>15</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Which is a complication of immobility the CNA observes and reports?</t>
+          <t>MCQ/TF</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>A) Pressure injury / skin breakdown  B) Improved appetite  C) Lower pulse  D) Faster healing</t>
+          <t>Which is an OBJECTIVE observation?</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Resident ate 50% of lunch</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Immobility raises risk of pressure injuries; observe and report.</t>
+          <t>Objective = measurable/observed fact; others are subjective/diagnostic.</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Review M13 complications of immobility (L13.6).</t>
+          <t>Route to U08 lesson review (source Module 15).</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -4565,47 +6444,47 @@
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>Full key</t>
+          <t>Full internal key</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>KC-M14-01</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
+          <t>KC-U09-01</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>U09</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>15</v>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Restorative care for a resident who can do part of their ADLs means the CNA should:</t>
+          <t>MCQ/TF</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>A) Do everything for them  B) Assist only as needed and encourage independence  C) Skip the ADL  D) Rush them</t>
+          <t>A CNA may chart 'resident has pneumonia' based on a cough.</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>False</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>Restorative philosophy promotes maximum independence.</t>
+          <t>CNAs document observations, not diagnoses.</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Review M14 restorative philosophy &amp; self-care (L14.1-L14.3).</t>
+          <t>Route to U09 lesson review (source Module 15).</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -4615,47 +6494,47 @@
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>Full key</t>
+          <t>Full internal key</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>KC-M14-02</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Matching</t>
-        </is>
+          <t>KC-U10-01</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>16</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Match adaptive/comfort device to its purpose.</t>
+          <t>MCQ/TF</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Trochanter roll / Foot board / Bed cradle / Heel protector (purposes provided)</t>
+          <t>A dying resident's family member is angry at staff. Best CNA response?</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Correct pairings per source</t>
+          <t>Respond with compassion, listen, and report concerns to the nurse</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Devices prevent complications and aid mobility.</t>
+          <t>Compassionate, scope-safe support; escalate appropriately.</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Review M14 devices (L14.4).</t>
+          <t>Route to U10 lesson review (source Module 16).</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -4665,47 +6544,47 @@
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>Full key</t>
+          <t>Full internal key</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>KC-M15-01</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
+          <t>KC-U11-01</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>17</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Which is an OBJECTIVE observation?</t>
+          <t>MCQ/TF</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>A) 'Resident seems sad'  B) 'Resident ate 50% of lunch'  C) 'Resident is depressed'  D) 'Resident is fine'</t>
+          <t>Which is an example of involuntary seclusion / a resident-rights violation?</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Confining a resident to a room against their will as punishment</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>Objective = measurable/observed fact; others are subjective/diagnostic.</t>
+          <t>Involuntary seclusion is a form of abuse/rights violation.</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Review M15 objective vs subjective (L15.3).</t>
+          <t>Route to U11 lesson review (source Module 17).</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -4715,47 +6594,47 @@
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>Full key</t>
+          <t>Full internal key</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>KC-M15-02</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>True/False</t>
-        </is>
+          <t>KC-U12-01</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>17</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>A CNA may chart 'resident has pneumonia' based on a cough.</t>
+          <t>MCQ/TF</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>True / False</t>
+          <t>A CNA witnesses a coworker handling a resident roughly and threatening them. The CNA must:</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Ensure resident safety and report immediately per mandated-reporter duty</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>CNAs document observations, not diagnoses.</t>
+          <t>CNAs are mandated reporters; ensure safety and report promptly.</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Review M15 scope-safe recording (L15.5).</t>
+          <t>Route to U12 lesson review (source Module 17).</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -4765,207 +6644,7 @@
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>Full key</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>KC-M16-01</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Matching</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Match the Kubler-Ross grief stage to its description.</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Denial / Anger / Bargaining / Depression / Acceptance (descriptions provided)</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Correct pairings per source</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>Five stages of grief per source.</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>Review M16 grief stages (L16.2).</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>Score + remediation only</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>Full key</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>KC-M16-02</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>A dying resident's family member is angry at staff. Best CNA response?</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>A) Argue back  B) Respond with compassion, listen, and report concerns to the nurse  C) Ignore them  D) Leave the unit</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>Compassionate, scope-safe support; escalate appropriately.</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>Review M16 emotional/spiritual needs (L16.3).</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>Score + remediation only</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>Full key</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>KC-M17-01</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>A CNA witnesses a coworker handling a resident roughly and threatening them. The CNA must:</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>A) Say nothing  B) Ensure resident safety and report immediately per policy/mandated-reporter duty  C) Confront only the coworker  D) Wait a week</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>CNAs are mandated reporters; ensure safety and report promptly.</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Review M17 recognizing &amp; reporting (L17.5).</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>Score + remediation only</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>Full key</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>KC-M17-02</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Which is an example of involuntary seclusion / a resident-rights violation?</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>A) Offering activities  B) Confining a resident to a room against their will as punishment  C) Assisting to the dining room  D) Honoring a preference</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>Involuntary seclusion is a form of abuse/rights violation.</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>Review M17 abuse types &amp; resident rights (L17.2, L17.4).</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>Score + remediation only</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>Full key</t>
+          <t>Full internal key</t>
         </is>
       </c>
     </row>
@@ -4987,7 +6666,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
@@ -4997,14 +6676,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Certificate_Gate - certificate blocked until ALL items pass (Draft)</t>
+          <t>Certificate_Gate - blocked until ALL 12 units + both Years complete (Draft)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>DRAFT / PENDING APPROVAL - Do not advertise, issue certificates, or represent this course as approved until approval status, provider/course identifiers, and certificate wording are confirmed. Online CE only; not clinical hours. Fictional data only; no PHI.</t>
+          <t>DRAFT / PENDING APPROVAL - Do not advertise, issue certificates, or represent this course as approved until approval status, provider/course identifiers, and certificate wording are confirmed. Online CE only; no clinical hours. 12 units x 2 online CE hours = 24. Source backbone: Modules 10-17. Fictional data only; no PHI.</t>
         </is>
       </c>
     </row>
@@ -5107,12 +6786,12 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Year 1 modules complete</t>
+          <t>Year 1 units complete</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>M10-M13 all activities complete</t>
+          <t>U01-U06 all activities complete</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -5171,12 +6850,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Year 2 modules complete</t>
+          <t>Year 2 units complete</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>M14-M17 all activities complete</t>
+          <t>U07-U12 all activities complete</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -5240,7 +6919,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Minimum documented engaged time met</t>
+          <t>Minimum documented engaged time met (24 online CE hours)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -5342,7 +7021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5357,14 +7036,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Application_Packet_Checklist (Draft)</t>
+          <t>Application_Packet_Checklist (Draft) - 12 units x 2 hours</t>
         </is>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>DRAFT / PENDING APPROVAL - Do not advertise, issue certificates, or represent this course as approved until approval status, provider/course identifiers, and certificate wording are confirmed. Online CE only; not clinical hours. Fictional data only; no PHI.</t>
+          <t>DRAFT / PENDING APPROVAL - Do not advertise, issue certificates, or represent this course as approved until approval status, provider/course identifiers, and certificate wording are confirmed. Online CE only; no clinical hours. 12 units x 2 online CE hours = 24. Source backbone: Modules 10-17. Fictional data only; no PHI.</t>
         </is>
       </c>
     </row>
@@ -5408,7 +7087,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Course outline (Modules 10-17)</t>
+          <t>Course outline (12 units x 2 hours)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -5423,12 +7102,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>This package Section M; _source_text/module-10..17</t>
+          <t>24_HOUR_CNA_COURSE_MATRIX_FINAL.md; CDPH_192B_COURSE_LIST_ATTACHMENT.md</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>CDPH-facing structure decision (Unit vs Module)</t>
+          <t>None (structure aligned)</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -5438,7 +7117,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Top open item #1</t>
+          <t>12 units U01-U12; Modules 10-17 source backbone</t>
         </is>
       </c>
     </row>
@@ -5460,12 +7139,12 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Section D</t>
+          <t>Section D / matrix</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Whether CDPH wants source-proportional or normalized hours</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -5475,7 +7154,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Even 3h x 8 used as draft</t>
+          <t>12 units x 2 hours = 24</t>
         </is>
       </c>
     </row>
@@ -5512,14 +7191,14 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>12 / 12 split</t>
+          <t>U01-U06 / U07-U12 (12 / 12)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Module mapping table</t>
+          <t>Unit-to-source mapping</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -5549,7 +7228,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Source titles preserved</t>
+          <t>Each unit maps to source Module 10-17</t>
         </is>
       </c>
     </row>
@@ -5571,7 +7250,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Section N</t>
+          <t>Course package</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -5586,7 +7265,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Marked Draft-Pending Approval</t>
+          <t>Marked Draft - Pending Approval</t>
         </is>
       </c>
     </row>
@@ -5608,7 +7287,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Section O</t>
+          <t>Course package</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -5645,7 +7324,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Section P</t>
+          <t>Course package</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -5663,7 +7342,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Attendance/proof-of-participation policy</t>
+          <t>Recordkeeping policy</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -5678,12 +7357,12 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Section M.10 / Q</t>
+          <t>Section L</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Exact seat-time definition</t>
+          <t>Retention period (CDPH vs BPPE)</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -5691,32 +7370,36 @@
           <t>Pending</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>12-unit completion evidence</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Learner attestation/affidavit</t>
+          <t>Refund / cancellation policy</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Placeholder</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Owner/Legal</t>
+          <t>Owner/Finance</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Section L / M.11</t>
+          <t>BPPE refund/pro-rata source files</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>CNA # requirement; legal review</t>
+          <t>Pull institution's approved policy</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -5724,12 +7407,16 @@
           <t>Pending</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Placeholder only</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Recordkeeping policy</t>
+          <t>SME/instructor of record</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -5739,17 +7426,17 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Owner/LMS admin</t>
+          <t>SME/Compliance</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Section Q</t>
+          <t>__Master-Application-Packet/01_CNA_CDPH_CE_PACKET/</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Retention period (CDPH vs BPPE)</t>
+          <t>Vanessa Valerio evidence attachment (resume/CV, license, expiration)</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -5757,32 +7444,36 @@
           <t>Pending</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Vanessa Valerio assigned; evidence is final verification</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Refund / cancellation policy</t>
+          <t>Provider/course approval evidence</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Placeholder</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Owner/Finance</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>BPPE refund/pro-rata source files (01_SOURCE_INVENTORY.md)</t>
+          <t>__Master-Application-Packet/01_CNA_CDPH_CE_PACKET/</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Pull institution's approved policy</t>
+          <t>No approved provider/course # issued</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -5791,179 +7482,6 @@
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>Placeholder only</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Advertising compliance checklist</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Compliance</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Section T</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>LMS evidence checklist</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>LMS admin</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Section Q</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>SME/compliance review checklist</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>SME/Compliance</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Sections T &amp; U</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>SME of record sign-off</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>__Master-Application-Packet/01_CNA_CDPH_CE_PACKET/ references Vanessa Valerio for CNA lane - confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Owner approval checklist</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Section W</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Provider/course approval evidence</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>__Master-Application-Packet/01_CNA_CDPH_CE_PACKET/</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>No approved provider/course # for Modules 10-17 lane found</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Course stays Draft until obtained</t>
         </is>
@@ -5983,11 +7501,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="44" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -5999,14 +7517,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SME_Compliance_Flags (Draft)</t>
+          <t>SME_Compliance_Flags (Draft) - source-hour normalization flagged only if clinically necessary</t>
         </is>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>DRAFT / PENDING APPROVAL - Do not advertise, issue certificates, or represent this course as approved until approval status, provider/course identifiers, and certificate wording are confirmed. Online CE only; not clinical hours. Fictional data only; no PHI.</t>
+          <t>DRAFT / PENDING APPROVAL - Do not advertise, issue certificates, or represent this course as approved until approval status, provider/course identifiers, and certificate wording are confirmed. Online CE only; no clinical hours. 12 units x 2 online CE hours = 24. Source backbone: Modules 10-17. Fictional data only; no PHI.</t>
         </is>
       </c>
     </row>
@@ -6018,7 +7536,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Source Module #</t>
+          <t>Unit / Source Module</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -6055,7 +7573,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>F-STRUCT</t>
+          <t>F-APPROVAL</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -6065,12 +7583,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Compliance/Structure</t>
+          <t>Compliance</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Master packet official allocation is 12 Units x 2h, not Modules 10-17</t>
+          <t>No approved provider/course number; certificate/advertising are Draft</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -6080,12 +7598,12 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Owner + SME + CDPH</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Resolve which structure is submitted; reconcile before any CDPH use</t>
+          <t>Obtain approval before issuing/advertising</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -6097,7 +7615,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>F-HOURS</t>
+          <t>F-NORM</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -6107,27 +7625,27 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Compliance</t>
+          <t>Clinical normalization</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Even 3h/module is normalized; source CCCCO theory hours are uneven</t>
+          <t>Source CCCCO theory hours are uneven; the CE build normalizes to 2 hours/unit. Flag only if a specific unit needs more time for clinical accuracy.</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>SME/CDPH</t>
+          <t>Clinical SME</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Confirm expected hour basis</t>
+          <t>Confirm 2-hour unit time is clinically sufficient per unit; adjust content depth, not structure</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -6139,37 +7657,37 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>F-APPROVAL</t>
+          <t>F-U01U02</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>U01-U02 / M10</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Compliance</t>
+          <t>Clinical accuracy</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>No approved provider/course number; certificate/advertising are Draft</t>
+          <t>Vital-signs ranges/factors must match current standards</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Clinical SME</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Obtain approval before issuing/advertising</t>
+          <t>Verify ranges; observe/report framing</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -6181,11 +7699,13 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>F-M10</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>10</v>
+          <t>F-U03</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>U03 / M11</t>
+        </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -6194,7 +7714,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Vital-signs normal ranges must match current standards</t>
+          <t>Therapeutic-diet list and aspiration precautions</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -6209,7 +7729,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Verify ranges/factors; ensure observe/report framing</t>
+          <t>Confirm vs facility diet manual; assistance level only</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -6221,25 +7741,27 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>F-M11</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>11</v>
+          <t>F-U04</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>U04 / M12</t>
+        </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Clinical accuracy</t>
+          <t>Scope/Clinical</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Therapeutic-diet list and aspiration precautions</t>
+          <t>Must not imply hands-on CPR/Heimlich certification</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -6249,7 +7771,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Confirm vs facility diet manual; assistance level only</t>
+          <t>Explicit disclaimer; verify codes + AHA/ARC language</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -6261,25 +7783,27 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>F-M12</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>12</v>
+          <t>F-U05U06</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>U05-U06 / M13</t>
+        </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Scope/Clinical</t>
+          <t>Scope/Content</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Must not imply hands-on CPR/Heimlich certification</t>
+          <t>Dementia-sensitive person-centered language; aging/A&amp;P accuracy</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -6289,7 +7813,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Add explicit disclaimer; verify codes + AHA/ARC language</t>
+          <t>Confirm person-centered language; CNA scope (no diagnosis)</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -6301,20 +7825,22 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>F-M13</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>13</v>
+          <t>F-U07</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>U07 / M14</t>
+        </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Scope/Content</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Dementia-sensitive language; SNF/ICF hour variant</t>
+          <t>ROM/restorative must stay assist/observe level</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -6329,7 +7855,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Confirm person-centered language and hour variant</t>
+          <t>No independent-therapy claim; confirm devices</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -6341,35 +7867,37 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>F-M14</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>14</v>
+          <t>F-U08U09</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>U08-U09 / M15</t>
+        </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>PHI/Scope</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>ROM/restorative must stay assist/observe level</t>
+          <t>Charting units; observations not diagnoses; PHI risk</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Clinical SME</t>
+          <t>SME/Compliance</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Ensure no independent-therapy claim; confirm devices</t>
+          <t>Reinforce no-PHI + objective documentation rules</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -6381,35 +7909,37 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>F-M15</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>15</v>
+          <t>F-U10</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>U10 / M16</t>
+        </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>PHI/Scope</t>
+          <t>Sensitivity/Scope</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Charting module; observations not diagnoses; PHI risk</t>
+          <t>End-of-life content; postmortem boundaries; no pronouncement of death</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>SME/Compliance</t>
+          <t>Clinical SME</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>Reinforce no-PHI + objective documentation rules</t>
+          <t>Add sensitivity note; confirm postmortem steps</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -6421,35 +7951,37 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>F-M16</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>16</v>
+          <t>F-U11U12</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>U11-U12 / M17</t>
+        </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Sensitivity/Scope</t>
+          <t>Legal/Compliance</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>End-of-life content; no pronouncement of death</t>
+          <t>CA mandated-reporter channels, timelines, ombudsman framing</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Clinical SME</t>
+          <t>Compliance/Legal</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Add sensitivity note; confirm postmortem steps</t>
+          <t>Verify current CA reporting requirements</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -6461,20 +7993,22 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>F-M17</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>17</v>
+          <t>F-PHI</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Legal/Compliance</t>
+          <t>Privacy</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>CA mandated-reporter channels, timelines, ombudsman framing</t>
+          <t>No real resident/facility data anywhere; fictional only</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -6484,57 +8018,15 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Compliance/Legal</t>
+          <t>Compliance</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>Verify current CA reporting requirements</t>
+          <t>Verify banners/agreements; periodic free-text review</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>F-PHI</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Privacy</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>No real resident/facility data anywhere; fictional only</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Compliance</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>Verify banners/agreements; periodic free-text review</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6569,14 +8061,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Audit_Evidence_Log (Draft)</t>
+          <t>Audit_Evidence_Log (Draft) - 12-unit completion evidence</t>
         </is>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>DRAFT / PENDING APPROVAL - Do not advertise, issue certificates, or represent this course as approved until approval status, provider/course identifiers, and certificate wording are confirmed. Online CE only; not clinical hours. Fictional data only; no PHI.</t>
+          <t>DRAFT / PENDING APPROVAL - Do not advertise, issue certificates, or represent this course as approved until approval status, provider/course identifiers, and certificate wording are confirmed. Online CE only; no clinical hours. 12 units x 2 online CE hours = 24. Source backbone: Modules 10-17. Fictional data only; no PHI.</t>
         </is>
       </c>
     </row>
@@ -6657,12 +8149,12 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Activity completion data</t>
+          <t>Unit completion data (U01-U12)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Module activities</t>
+          <t>Unit activities</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -6685,7 +8177,11 @@
           <t>Completion report (CSV)</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>12 units x 2 hours</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -6727,7 +8223,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Knowledge-check attempts</t>
+          <t>Knowledge-check attempts (KC-U01..U12)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -6801,7 +8297,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Scenario decision logs</t>
+          <t>Scenario decision logs (S-U01..U12)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
